--- a/artfynd/A 40422-2022 artfynd.xlsx
+++ b/artfynd/A 40422-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40422-2022 artfynd.xlsx
+++ b/artfynd/A 40422-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15878824</v>
+        <v>15878874</v>
       </c>
       <c r="B2" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövkärr S Asketorpegölen, Ög</t>
+          <t>S Asketorpegölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549495.3553707569</v>
+        <v>549615</v>
       </c>
       <c r="R2" t="n">
-        <v>6459932.170721121</v>
+        <v>6459984</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-05-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-05-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-16</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På ved i lövkärr.</t>
+          <t>På ved i sumpskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15878874</v>
+        <v>15878824</v>
       </c>
       <c r="B3" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>S Asketorpegölen, Ög</t>
+          <t>Lövkärr S Asketorpegölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549614.8486119059</v>
+        <v>549495</v>
       </c>
       <c r="R3" t="n">
-        <v>6459983.63448504</v>
+        <v>6459932</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -862,27 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-11-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-11-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-05-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På ved i sumpskog.</t>
+          <t>På ved i lövkärr.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,12 +882,7 @@
         <v>15878878</v>
       </c>
       <c r="B4" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549614.8486119059</v>
+        <v>549615</v>
       </c>
       <c r="R4" t="n">
-        <v>6459983.63448504</v>
+        <v>6459984</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,19 +947,9 @@
           <t>2013-11-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-11-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,53 +981,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>15878835</v>
+        <v>132064372</v>
       </c>
       <c r="B5" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>220075</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>S Asketorpegölen, Ög</t>
+          <t>S Asketorpegölen, S Asketorpegölen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549614.8486119059</v>
+        <v>549628</v>
       </c>
       <c r="R5" t="n">
-        <v>6459983.63448504</v>
+        <v>6459950</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,27 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-05-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-05-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 10 stånd i blöt sumpskog söder om och något högre än Asketorpegölen. Talrika körskador, värdefullt om sumpskogen kan lämnas opåverkad i framtiden.</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15878826</v>
+        <v>15878835</v>
       </c>
       <c r="B6" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,34 +1103,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövkärr S Asketorpegölen, Ög</t>
+          <t>S Asketorpegölen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549495.3553707569</v>
+        <v>549615</v>
       </c>
       <c r="R6" t="n">
-        <v>6459932.170721121</v>
+        <v>6459984</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,24 +1160,14 @@
           <t>2013-05-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-05-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Lövkärr med rörligt markvatten.</t>
+          <t>Ca 10 stånd i blöt sumpskog söder om och något högre än Asketorpegölen. Talrika körskador, värdefullt om sumpskogen kan lämnas opåverkad i framtiden.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,6 +1191,219 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>15878826</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lövkärr S Asketorpegölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>549495</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6459932</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2013-05-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2013-05-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lövkärr med rörligt markvatten.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132064424</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>S Asketorpegölen, S Asketorpegölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>549628</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6459950</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40422-2022 artfynd.xlsx
+++ b/artfynd/A 40422-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15878874</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15878824</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15878878</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132064372</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15878835</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15878826</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,8 +1439,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132064424</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>